--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.60528708727454</v>
+        <v>2.860859151682113</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61575074165532</v>
+        <v>2.700059495518989</v>
       </c>
       <c r="E2" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F2" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.52027794030212</v>
+        <v>2.684545165299094</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72094704024691</v>
+        <v>2.717153894040122</v>
       </c>
       <c r="E3" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F3" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.23543122605953</v>
+        <v>1.825757574234674</v>
       </c>
       <c r="D4" t="n">
-        <v>12.33697365561529</v>
+        <v>2.004758219037485</v>
       </c>
       <c r="E4" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F4" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.07537253608807</v>
+        <v>2.612248037114312</v>
       </c>
       <c r="D5" t="n">
-        <v>16.85949541492901</v>
+        <v>2.739668004925964</v>
       </c>
       <c r="E5" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F5" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.70311746193934</v>
+        <v>3.039256587565142</v>
       </c>
       <c r="D6" t="n">
-        <v>19.7297684614875</v>
+        <v>3.206087374991719</v>
       </c>
       <c r="E6" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F6" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.11275343993009</v>
+        <v>3.43082243398864</v>
       </c>
       <c r="D7" t="n">
-        <v>21.54430590642028</v>
+        <v>3.500949709793296</v>
       </c>
       <c r="E7" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F7" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.89707381993651</v>
+        <v>8.108274495739684</v>
       </c>
       <c r="D8" t="n">
-        <v>49.71322884904875</v>
+        <v>8.078399687970421</v>
       </c>
       <c r="E8" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F8" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.39197826910429</v>
+        <v>8.513696468729446</v>
       </c>
       <c r="D9" t="n">
-        <v>51.89887298170918</v>
+        <v>8.43356685952774</v>
       </c>
       <c r="E9" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F9" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.57736633062447</v>
+        <v>6.918822028726477</v>
       </c>
       <c r="D10" t="n">
-        <v>41.96244664778287</v>
+        <v>6.818897580264716</v>
       </c>
       <c r="E10" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F10" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.28360187542624</v>
+        <v>4.596085304756764</v>
       </c>
       <c r="D11" t="n">
-        <v>12.24563567364732</v>
+        <v>1.989915796967689</v>
       </c>
       <c r="E11" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F11" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.73710301497194</v>
+        <v>4.83227923993294</v>
       </c>
       <c r="D12" t="n">
-        <v>28.87535674944602</v>
+        <v>4.692245471784978</v>
       </c>
       <c r="E12" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F12" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.34338748580804</v>
+        <v>8.668300466443808</v>
       </c>
       <c r="D13" t="n">
-        <v>52.54946376001835</v>
+        <v>8.539287861002983</v>
       </c>
       <c r="E13" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F13" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.15979840832685</v>
+        <v>7.175967241353113</v>
       </c>
       <c r="D14" t="n">
-        <v>42.92899110606148</v>
+        <v>6.975961054734991</v>
       </c>
       <c r="E14" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F14" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.40870792436451</v>
+        <v>5.753915037709234</v>
       </c>
       <c r="D15" t="n">
-        <v>34.22971385779098</v>
+        <v>5.562328501891035</v>
       </c>
       <c r="E15" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F15" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>52.24435990600767</v>
+        <v>8.489708484726247</v>
       </c>
       <c r="D16" t="n">
-        <v>31.5631062766345</v>
+        <v>5.129004769953107</v>
       </c>
       <c r="E16" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F16" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>65.24411323309596</v>
+        <v>10.60216840037809</v>
       </c>
       <c r="D17" t="n">
-        <v>63.97844647414747</v>
+        <v>10.39649755204896</v>
       </c>
       <c r="E17" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F17" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>56.46406578156188</v>
+        <v>9.175410689503806</v>
       </c>
       <c r="D18" t="n">
-        <v>55.05872002698036</v>
+        <v>8.94704200438431</v>
       </c>
       <c r="E18" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F18" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>60.53205938464954</v>
+        <v>9.836459650005551</v>
       </c>
       <c r="D19" t="n">
-        <v>51.69320881799186</v>
+        <v>8.400146432923677</v>
       </c>
       <c r="E19" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F19" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>67.98044005403609</v>
+        <v>11.04682150878087</v>
       </c>
       <c r="D20" t="n">
-        <v>66.58160800222137</v>
+        <v>10.81951130036097</v>
       </c>
       <c r="E20" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F20" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>74.7141219048053</v>
+        <v>12.14104480953086</v>
       </c>
       <c r="D21" t="n">
-        <v>59.79714348157837</v>
+        <v>9.717035815756486</v>
       </c>
       <c r="E21" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F21" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>68.3083000199274</v>
+        <v>11.1000987532382</v>
       </c>
       <c r="D22" t="n">
-        <v>67.01617858520592</v>
+        <v>10.89012902009596</v>
       </c>
       <c r="E22" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F22" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>70.59675113975401</v>
+        <v>11.47197206021003</v>
       </c>
       <c r="D23" t="n">
-        <v>69.2254250882348</v>
+        <v>11.24913157683816</v>
       </c>
       <c r="E23" t="n">
-        <v>20.1610230010023</v>
+        <v>3.276166237662874</v>
       </c>
       <c r="F23" t="n">
-        <v>19.2659305390996</v>
+        <v>3.130713712603685</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
